--- a/Solution_recipes/DS_SS_highSalt_Relax/1M_KI_Relax.xlsx
+++ b/Solution_recipes/DS_SS_highSalt_Relax/1M_KI_Relax.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minto\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minto\Documents\GitHub\Protocols\Solution_recipes\DS_SS_highSalt_Relax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612221C1-6E79-4FE1-A60A-DE6363B46022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610A0834-A009-49EC-B689-4A75B5012FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9450" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KI" sheetId="2" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Made by</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>14 mL</t>
-  </si>
-  <si>
-    <t>7 ml</t>
   </si>
   <si>
     <t>Target pH = 7.00</t>
@@ -162,6 +159,15 @@
   </si>
   <si>
     <t>1 M KI - High-Salt Relax</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>concentration (mM)</t>
+  </si>
+  <si>
+    <t>7 mL</t>
   </si>
 </sst>
 </file>
@@ -210,7 +216,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -496,11 +502,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -608,6 +640,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -966,7 +1004,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="30"/>
     </row>
@@ -993,22 +1031,22 @@
         <v>4</v>
       </c>
       <c r="D4" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="G4" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="18" t="s">
-        <v>23</v>
-      </c>
       <c r="H4" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="18" t="s">
         <v>18</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>19</v>
       </c>
       <c r="J4" s="20" t="s">
         <v>5</v>
@@ -1016,7 +1054,7 @@
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1121,9 +1159,13 @@
       <c r="B9" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="C9" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="38"/>
       <c r="F9" s="22" t="s">
         <v>11</v>
       </c>
@@ -1134,32 +1176,32 @@
         <v>12</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J9" s="24"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:10" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="9"/>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="17"/>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="34"/>
     </row>
@@ -1193,11 +1235,12 @@
     <row r="72" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="73" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -1205,14 +1248,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6cbc0c5a-d948-46e5-8624-1bad210f77c7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1224,12 +1265,14 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6cbc0c5a-d948-46e5-8624-1bad210f77c7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1488,12 +1531,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3012E31E-5C99-4C5B-9323-B5D42B3C4F74}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{576E4525-D34E-471F-91EB-AF7A16356FDF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a"/>
-    <ds:schemaRef ds:uri="6cbc0c5a-d948-46e5-8624-1bad210f77c7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1507,9 +1547,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{576E4525-D34E-471F-91EB-AF7A16356FDF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3012E31E-5C99-4C5B-9323-B5D42B3C4F74}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5d5a2885-0f9b-4d04-9bc1-f867a2376b8a"/>
+    <ds:schemaRef ds:uri="6cbc0c5a-d948-46e5-8624-1bad210f77c7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
